--- a/results/LCA/lci_comparison_ab/graphite_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/graphite_LCIA-results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
   <si>
     <t>index</t>
   </si>
@@ -43,82 +43,91 @@
     <t>IMPACT World+ Damage 2.1 for ecoinvent v3.10 | Ecosystem quality | Total ecosystem quality</t>
   </si>
   <si>
-    <t>battery-grade graphite | [P+R] Synthetic graphite production | CN | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>graphite ore, mined | market for graphite ore, mined | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>graphite ore, mined | graphite ore mining | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>battery-grade graphite | graphite (C) global market | GLO | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>graphite | market for graphite | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>graphite ore, concentrated | natural graphite concentration | CN | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>battery-grade graphite | graphite ore mining in China/Heilongjiang and natural graphite production in China/Shandong | CN | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>graphite | graphite production | CA | kilogram | premise_generated_db_2025_L</t>
+    <t>graphite | market for graphite | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>battery-grade graphite | [P+R] Synthetic graphite production | CN | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>battery-grade graphite | graphite ore mining in China/Heilongjiang and natural graphite production in China/Shandong | CN | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>graphite ore, mined | graphite ore mining | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>battery-grade graphite | graphite (C) global market | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>graphite ore | [M] Graphite ore mining | CN | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>graphite | graphite production | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>graphite ore, mined | market for graphite ore, mined | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>graphite concentrate | [C] Flotation | CN | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>kilogram</t>
   </si>
   <si>
+    <t>graphite</t>
+  </si>
+  <si>
     <t>battery-grade graphite</t>
   </si>
   <si>
     <t>graphite ore, mined</t>
   </si>
   <si>
-    <t>graphite</t>
-  </si>
-  <si>
-    <t>graphite ore, concentrated</t>
+    <t>graphite ore</t>
+  </si>
+  <si>
+    <t>graphite concentrate</t>
+  </si>
+  <si>
+    <t>market for graphite</t>
   </si>
   <si>
     <t>[P+R] Synthetic graphite production</t>
   </si>
   <si>
+    <t>graphite ore mining in China/Heilongjiang and natural graphite production in China/Shandong</t>
+  </si>
+  <si>
+    <t>graphite ore mining</t>
+  </si>
+  <si>
+    <t>graphite (C) global market</t>
+  </si>
+  <si>
+    <t>[M] Graphite ore mining</t>
+  </si>
+  <si>
+    <t>graphite production</t>
+  </si>
+  <si>
     <t>market for graphite ore, mined</t>
   </si>
   <si>
-    <t>graphite ore mining</t>
-  </si>
-  <si>
-    <t>graphite (C) global market</t>
-  </si>
-  <si>
-    <t>market for graphite</t>
-  </si>
-  <si>
-    <t>natural graphite concentration</t>
-  </si>
-  <si>
-    <t>graphite ore mining in China/Heilongjiang and natural graphite production in China/Shandong</t>
-  </si>
-  <si>
-    <t>graphite production</t>
+    <t>[C] Flotation</t>
+  </si>
+  <si>
+    <t>World</t>
   </si>
   <si>
     <t>CN</t>
   </si>
   <si>
-    <t>World</t>
-  </si>
-  <si>
     <t>CA</t>
   </si>
   <si>
     <t>GLO</t>
   </si>
   <si>
-    <t>premise_generated_db_2025_L</t>
+    <t>premise_db_2025_L</t>
   </si>
 </sst>
 </file>
@@ -476,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -519,25 +528,25 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>0.0001348909346679084</v>
+        <v>7.426275490767717E-07</v>
       </c>
       <c r="J2">
-        <v>14.23150557394004</v>
+        <v>0.1096677600427104</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -551,25 +560,25 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I3">
-        <v>1.268875723431444E-06</v>
+        <v>0.0001305696353052184</v>
       </c>
       <c r="J3">
-        <v>0.1762709217486588</v>
+        <v>14.21458366202601</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -583,25 +592,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I4">
-        <v>1.04658700279811E-07</v>
+        <v>5.37161962176232E-05</v>
       </c>
       <c r="J4">
-        <v>0.01222070708054277</v>
+        <v>5.992286551907412</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -615,25 +624,25 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>0.0001016662272918009</v>
+        <v>1.2185959392716E-07</v>
       </c>
       <c r="J5">
-        <v>10.79040267708415</v>
+        <v>0.01493117161151997</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -647,25 +656,25 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I6">
-        <v>1.330384561739204E-06</v>
+        <v>9.824685939105156E-05</v>
       </c>
       <c r="J6">
-        <v>0.1907648423731758</v>
+        <v>10.7564759871157</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -679,25 +688,25 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>5.336084441052017E-06</v>
+        <v>5.761202620606392E-08</v>
       </c>
       <c r="J7">
-        <v>0.6751103989386495</v>
+        <v>0.008463640274682421</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -711,25 +720,25 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I8">
-        <v>5.589298505613017E-05</v>
+        <v>1.624825162852842E-07</v>
       </c>
       <c r="J8">
-        <v>6.049640506971567</v>
+        <v>0.02955141766125667</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -743,25 +752,57 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9">
+        <v>6.886458865882077E-07</v>
+      </c>
+      <c r="J9">
+        <v>0.09333689673224806</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="H9" t="s">
+      <c r="G10" t="s">
         <v>34</v>
       </c>
-      <c r="I9">
-        <v>9.762850025673412E-08</v>
-      </c>
-      <c r="J9">
-        <v>0.0191500238235324</v>
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10">
+        <v>4.015910861533234E-06</v>
+      </c>
+      <c r="J10">
+        <v>0.5513600300741892</v>
       </c>
     </row>
   </sheetData>

--- a/results/LCA/lci_comparison_ab/graphite_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/graphite_LCIA-results.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/results/LCA/lci_comparison_ab/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_060102FAF613C8264F2C4CABE5F0831352503593" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC3C615-AA6E-470C-B7A5-A7C1F43D4A34}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -133,8 +142,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,12 +160,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -186,24 +201,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -241,7 +268,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -275,6 +302,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -309,9 +337,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,11 +513,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="86.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,12 +550,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -531,30 +564,30 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
       </c>
       <c r="I2">
-        <v>7.426275490767717E-07</v>
+        <v>1.2185959392716E-7</v>
       </c>
       <c r="J2">
-        <v>0.1096677600427104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>1.493117161151997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -563,30 +596,30 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
         <v>37</v>
       </c>
       <c r="I3">
-        <v>0.0001305696353052184</v>
+        <v>1.624825162852842E-7</v>
       </c>
       <c r="J3">
-        <v>14.21458366202601</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>2.9551417661256671E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -598,7 +631,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
         <v>34</v>
@@ -607,18 +640,18 @@
         <v>37</v>
       </c>
       <c r="I4">
-        <v>5.37161962176232E-05</v>
+        <v>1.305696353052184E-4</v>
       </c>
       <c r="J4">
-        <v>5.992286551907412</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>14.21458366202601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -627,126 +660,126 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>37</v>
       </c>
       <c r="I5">
-        <v>1.2185959392716E-07</v>
+        <v>5.3716196217623203E-5</v>
       </c>
       <c r="J5">
-        <v>0.01493117161151997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1">
+        <v>5.9922865519074122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5.7612026206063921E-8</v>
+      </c>
+      <c r="J6" s="3">
+        <v>8.4636402746824206E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="3">
+        <v>4.0159108615332338E-6</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.55136003007418921</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I6">
-        <v>9.824685939105156E-05</v>
-      </c>
-      <c r="J6">
-        <v>10.7564759871157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>5.761202620606392E-08</v>
-      </c>
-      <c r="J7">
-        <v>0.008463640274682421</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8">
-        <v>1.624825162852842E-07</v>
-      </c>
-      <c r="J8">
-        <v>0.02955141766125667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="I8" s="3">
+        <v>9.8246859391051562E-5</v>
+      </c>
+      <c r="J8" s="3">
+        <v>10.756475987115699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -755,10 +788,10 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
         <v>33</v>
@@ -767,18 +800,18 @@
         <v>37</v>
       </c>
       <c r="I9">
-        <v>6.886458865882077E-07</v>
+        <v>7.4262754907677165E-7</v>
       </c>
       <c r="J9">
-        <v>0.09333689673224806</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>0.10966776004271039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -787,25 +820,30 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
       </c>
       <c r="I10">
-        <v>4.015910861533234E-06</v>
+        <v>6.886458865882077E-7</v>
       </c>
       <c r="J10">
-        <v>0.5513600300741892</v>
+        <v>9.3336896732248056E-2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J10">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>